--- a/clima.xlsx
+++ b/clima.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -644,6 +644,469 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Minsk</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>226</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Muy nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>155</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>noche</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Muy nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>532</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Parcialmente nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Quito</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2858</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>noche</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Quito</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2858</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Muy nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>roma</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Muy nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>paris</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>43</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Parcialmente nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>peru</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ayacucho</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2743</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Muy nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>madrid</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>651</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Parcialmente nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>madrid</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>651</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Noreste</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>colombia</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>bogotá</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>608</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>noche</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Muy nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>651</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Noreste</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>651</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Noreste</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Nublado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/clima.xlsx
+++ b/clima.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -1071,6 +1071,78 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" t="n">
+        <v>651</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Nublado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Santa fe</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>23</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Día</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sureste</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Muy nublado</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
